--- a/xls.xlsx
+++ b/xls.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="4">
   <si>
     <t>aa</t>
   </si>
@@ -36,9 +36,6 @@
   </si>
   <si>
     <t>cc</t>
-  </si>
-  <si>
-    <t>dd</t>
   </si>
   <si>
     <t>xx</t>
@@ -676,10 +673,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1001,8 +998,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <dimension ref="A2:I22"/>
+  <sheetFormatPr defaultColWidth="9.14166666666667" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.2333333333333" style="1" customWidth="1"/>
@@ -1011,13 +1008,13 @@
     <col min="5" max="16384" width="9.14166666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" ht="15" spans="1:4">
+    <row r="3" ht="15" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1027,125 +1024,280 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" ht="15" spans="1:4">
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" ht="15" spans="1:4">
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="15" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" ht="15" spans="1:4">
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" ht="15" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" ht="15" spans="1:4">
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" ht="15" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" ht="15" spans="1:4">
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" ht="15" spans="1:4">
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" ht="15" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" ht="15" spans="1:4">
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" ht="15" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" ht="15" spans="1:4">
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" ht="15" spans="1:4">
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" ht="15" spans="1:9">
       <c r="A15" s="3"/>
-      <c r="B15" s="5"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" ht="15" spans="1:4">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" ht="15" spans="1:9">
       <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="18" ht="15" spans="1:4">
       <c r="A18" s="3"/>
@@ -1155,15 +1307,15 @@
     </row>
     <row r="19" ht="15" spans="1:4">
       <c r="A19" s="3"/>
-      <c r="B19" s="5"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="5"/>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" ht="15" spans="1:4">
       <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="3"/>
